--- a/sample_data/output/excel/02_수도권별_유형집계.xlsx
+++ b/sample_data/output/excel/02_수도권별_유형집계.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,19 +483,19 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>21</v>
+        <v>160</v>
       </c>
       <c r="F2" t="n">
-        <v>3338.1999</v>
+        <v>221678.271992234</v>
       </c>
       <c r="G2" t="n">
-        <v>1247.761904761905</v>
+        <v>1228.11875</v>
       </c>
       <c r="H2" t="n">
-        <v>17127.61904761905</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4311027896464602</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -518,19 +518,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>9</v>
+        <v>78</v>
       </c>
       <c r="F3" t="n">
-        <v>1384.9899</v>
+        <v>97827.388699049</v>
       </c>
       <c r="G3" t="n">
-        <v>777</v>
+        <v>1043.192307692308</v>
       </c>
       <c r="H3" t="n">
-        <v>121372.2222222222</v>
+        <v>60660.25641025641</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8826051966369035</v>
+        <v>0.8198865370873608</v>
       </c>
     </row>
     <row r="4">
@@ -553,19 +553,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>30</v>
+        <v>286</v>
       </c>
       <c r="F4" t="n">
-        <v>5005.001</v>
+        <v>417916.658603107</v>
       </c>
       <c r="G4" t="n">
-        <v>3454.633333333333</v>
+        <v>4157.898601398601</v>
       </c>
       <c r="H4" t="n">
-        <v>47781</v>
+        <v>2566.783216783217</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6217812197851307</v>
+        <v>0.1588162221035203</v>
       </c>
     </row>
     <row r="5">
@@ -588,19 +588,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>12</v>
+        <v>493</v>
       </c>
       <c r="F5" t="n">
-        <v>2448.8421</v>
+        <v>727148.795465857</v>
       </c>
       <c r="G5" t="n">
-        <v>4293.666666666667</v>
+        <v>7029.204868154158</v>
       </c>
       <c r="H5" t="n">
-        <v>120915.6666666667</v>
+        <v>73110.3448275862</v>
       </c>
       <c r="I5" t="n">
-        <v>0.84759969921496</v>
+        <v>0.6956595607070732</v>
       </c>
     </row>
     <row r="6">
@@ -623,19 +623,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>20</v>
+        <v>244</v>
       </c>
       <c r="F6" t="n">
-        <v>3928.6213</v>
+        <v>298023.428483664</v>
       </c>
       <c r="G6" t="n">
-        <v>1234.9</v>
+        <v>1137.286885245902</v>
       </c>
       <c r="H6" t="n">
-        <v>28753.8</v>
+        <v>75.40983606557377</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5522300509829244</v>
+        <v>0.01601050521898927</v>
       </c>
     </row>
     <row r="7">
@@ -658,19 +658,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>15</v>
+        <v>139</v>
       </c>
       <c r="F7" t="n">
-        <v>2663.2754</v>
+        <v>174259.505781497</v>
       </c>
       <c r="G7" t="n">
-        <v>766.8666666666667</v>
+        <v>825.2661870503597</v>
       </c>
       <c r="H7" t="n">
-        <v>116845.6</v>
+        <v>52548.43884892086</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8756835421595877</v>
+        <v>0.8886940058553187</v>
       </c>
     </row>
     <row r="8">
@@ -693,19 +693,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>40</v>
+        <v>140</v>
       </c>
       <c r="F8" t="n">
-        <v>6507.5474</v>
+        <v>177716.083009883</v>
       </c>
       <c r="G8" t="n">
-        <v>3992.8</v>
+        <v>2943.607142857143</v>
       </c>
       <c r="H8" t="n">
-        <v>56320.35</v>
+        <v>7125</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7053749487070227</v>
+        <v>0.3115993800869227</v>
       </c>
     </row>
     <row r="9">
@@ -728,19 +728,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>23</v>
+        <v>248</v>
       </c>
       <c r="F9" t="n">
-        <v>3569.5449</v>
+        <v>338001.542292387</v>
       </c>
       <c r="G9" t="n">
-        <v>5409.086956521739</v>
+        <v>4771.552419354839</v>
       </c>
       <c r="H9" t="n">
-        <v>116657.4347826087</v>
+        <v>83303.22580645161</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8727145000306045</v>
+        <v>0.7583940762693352</v>
       </c>
     </row>
     <row r="10">
@@ -763,19 +763,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>14</v>
+        <v>442</v>
       </c>
       <c r="F10" t="n">
-        <v>2494.12</v>
+        <v>272493.282306527</v>
       </c>
       <c r="G10" t="n">
-        <v>979.0714285714286</v>
+        <v>1280.35294117647</v>
       </c>
       <c r="H10" t="n">
-        <v>30393.85714285714</v>
+        <v>690.5656108597285</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5929994540731639</v>
+        <v>0.1233335738413891</v>
       </c>
     </row>
     <row r="11">
@@ -798,19 +798,19 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>14</v>
+        <v>121</v>
       </c>
       <c r="F11" t="n">
-        <v>2139.3416</v>
+        <v>84268.561814569</v>
       </c>
       <c r="G11" t="n">
-        <v>754.2142857142857</v>
+        <v>959.2892561983471</v>
       </c>
       <c r="H11" t="n">
-        <v>118665</v>
+        <v>25414.87603305785</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8830852012394176</v>
+        <v>0.7364870671191805</v>
       </c>
     </row>
     <row r="12">
@@ -833,19 +833,19 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>20</v>
+        <v>1181</v>
       </c>
       <c r="F12" t="n">
-        <v>4134.7666</v>
+        <v>857147.791811303</v>
       </c>
       <c r="G12" t="n">
-        <v>3758.15</v>
+        <v>3786.080440304826</v>
       </c>
       <c r="H12" t="n">
-        <v>50865.85</v>
+        <v>5560.016934801016</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6704439059523595</v>
+        <v>0.3331333397839507</v>
       </c>
     </row>
     <row r="13">
@@ -868,19 +868,19 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>12</v>
+        <v>884</v>
       </c>
       <c r="F13" t="n">
-        <v>2332.1825</v>
+        <v>660433.917131659</v>
       </c>
       <c r="G13" t="n">
-        <v>4984.333333333333</v>
+        <v>5412.648190045249</v>
       </c>
       <c r="H13" t="n">
-        <v>119138.5</v>
+        <v>32231.15384615385</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8785188619717589</v>
+        <v>0.594724632506627</v>
       </c>
     </row>
     <row r="14">
@@ -903,19 +903,19 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>21</v>
+        <v>873</v>
       </c>
       <c r="F14" t="n">
-        <v>3422.471</v>
+        <v>554035.945960442</v>
       </c>
       <c r="G14" t="n">
-        <v>1498.047619047619</v>
+        <v>1136.154639175258</v>
       </c>
       <c r="H14" t="n">
-        <v>19781.57142857143</v>
+        <v>856.6254295532646</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4335413228637253</v>
+        <v>0.1718875780098028</v>
       </c>
     </row>
     <row r="15">
@@ -938,19 +938,19 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>17</v>
+        <v>245</v>
       </c>
       <c r="F15" t="n">
-        <v>3553.5163</v>
+        <v>147337.097776641</v>
       </c>
       <c r="G15" t="n">
-        <v>835.5882352941177</v>
+        <v>1066.751020408163</v>
       </c>
       <c r="H15" t="n">
-        <v>113464.9411764706</v>
+        <v>26157.95918367347</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8847320838598047</v>
+        <v>0.8248754063648499</v>
       </c>
     </row>
     <row r="16">
@@ -973,19 +973,19 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>42</v>
+        <v>813</v>
       </c>
       <c r="F16" t="n">
-        <v>7116.9305</v>
+        <v>540315.884052027</v>
       </c>
       <c r="G16" t="n">
-        <v>4090.142857142857</v>
+        <v>2280.150061500615</v>
       </c>
       <c r="H16" t="n">
-        <v>47024.40476190476</v>
+        <v>6440.730627306273</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6747786466959618</v>
+        <v>0.484774659859344</v>
       </c>
     </row>
     <row r="17">
@@ -1008,19 +1008,19 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>29</v>
+        <v>367</v>
       </c>
       <c r="F17" t="n">
-        <v>4766.8935</v>
+        <v>251826.554230231</v>
       </c>
       <c r="G17" t="n">
-        <v>4955.172413793103</v>
+        <v>3756.427792915531</v>
       </c>
       <c r="H17" t="n">
-        <v>119822.0344827586</v>
+        <v>30739.23705722071</v>
       </c>
       <c r="I17" t="n">
-        <v>0.865534624989747</v>
+        <v>0.6767016328798695</v>
       </c>
     </row>
     <row r="18">
@@ -1043,19 +1043,19 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>16</v>
+        <v>152</v>
       </c>
       <c r="F18" t="n">
-        <v>3123.8669</v>
+        <v>205340.6416331</v>
       </c>
       <c r="G18" t="n">
-        <v>1893.9375</v>
+        <v>1139.861842105263</v>
       </c>
       <c r="H18" t="n">
-        <v>26649.5625</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6085742243577685</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1078,19 +1078,19 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>11</v>
+        <v>77</v>
       </c>
       <c r="F19" t="n">
-        <v>2097.4746</v>
+        <v>100720.2935279</v>
       </c>
       <c r="G19" t="n">
-        <v>1074.636363636364</v>
+        <v>1023.701298701299</v>
       </c>
       <c r="H19" t="n">
-        <v>125610.7272727273</v>
+        <v>50019.48051948052</v>
       </c>
       <c r="I19" t="n">
-        <v>0.879452842841586</v>
+        <v>0.8690255269303564</v>
       </c>
     </row>
     <row r="20">
@@ -1113,19 +1113,19 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>26</v>
+        <v>305</v>
       </c>
       <c r="F20" t="n">
-        <v>4669.6962</v>
+        <v>436430.9360359</v>
       </c>
       <c r="G20" t="n">
-        <v>3715.5</v>
+        <v>4237.875409836066</v>
       </c>
       <c r="H20" t="n">
-        <v>50494.3076923077</v>
+        <v>3622.032786885246</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6330120838891971</v>
+        <v>0.1831987803898601</v>
       </c>
     </row>
     <row r="21">
@@ -1148,19 +1148,19 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>19</v>
+        <v>511</v>
       </c>
       <c r="F21" t="n">
-        <v>3186.5667</v>
+        <v>739662.288369</v>
       </c>
       <c r="G21" t="n">
-        <v>5322.105263157895</v>
+        <v>7480.909980430529</v>
       </c>
       <c r="H21" t="n">
-        <v>118743.5789473684</v>
+        <v>74138.16046966732</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8705178281467411</v>
+        <v>0.6903049689441437</v>
       </c>
     </row>
     <row r="22">
@@ -1183,19 +1183,19 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>21</v>
+        <v>245</v>
       </c>
       <c r="F22" t="n">
-        <v>3198.2302</v>
+        <v>290051.5625374</v>
       </c>
       <c r="G22" t="n">
-        <v>1062.333333333333</v>
+        <v>1179.54693877551</v>
       </c>
       <c r="H22" t="n">
-        <v>24622.7619047619</v>
+        <v>104.4897959183673</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5219303766670202</v>
+        <v>0.02635643443269643</v>
       </c>
     </row>
     <row r="23">
@@ -1214,23 +1214,23 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>C유형_기타일반가구</t>
+          <t>B유형_자산소득불일치</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>46</v>
+        <v>123</v>
       </c>
       <c r="F23" t="n">
-        <v>7785.9003</v>
+        <v>154685.0889611</v>
       </c>
       <c r="G23" t="n">
-        <v>4311.804347826087</v>
+        <v>1060.934959349594</v>
       </c>
       <c r="H23" t="n">
-        <v>49123.36956521739</v>
+        <v>49756.91056910569</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6733334235396589</v>
+        <v>0.9016057776266224</v>
       </c>
     </row>
     <row r="24">
@@ -1249,23 +1249,23 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>D유형_여유자산가층</t>
+          <t>C유형_기타일반가구</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>25</v>
+        <v>158</v>
       </c>
       <c r="F24" t="n">
-        <v>3472.6491</v>
+        <v>201730.6259339</v>
       </c>
       <c r="G24" t="n">
-        <v>4459.92</v>
+        <v>2763.955696202532</v>
       </c>
       <c r="H24" t="n">
-        <v>110001.6</v>
+        <v>8446.139240506329</v>
       </c>
       <c r="I24" t="n">
-        <v>0.8234897942377285</v>
+        <v>0.3166170131694451</v>
       </c>
     </row>
     <row r="25">
@@ -1274,33 +1274,33 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>G2</t>
+          <t>G1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>전기고령자(65-74)</t>
+          <t>후기고령자(75+)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>A유형_구조적취약층</t>
+          <t>D유형_여유자산가층</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6</v>
+        <v>287</v>
       </c>
       <c r="F25" t="n">
-        <v>862.0281</v>
+        <v>388803.6549805</v>
       </c>
       <c r="G25" t="n">
-        <v>1887.666666666667</v>
+        <v>5323.787456445993</v>
       </c>
       <c r="H25" t="n">
-        <v>30916.33333333333</v>
+        <v>86987.45644599303</v>
       </c>
       <c r="I25" t="n">
-        <v>0.5759891307735463</v>
+        <v>0.7472500959198682</v>
       </c>
     </row>
     <row r="26">
@@ -1319,23 +1319,23 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>B유형_자산소득불일치</t>
+          <t>A유형_구조적취약층</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>12</v>
+        <v>405</v>
       </c>
       <c r="F26" t="n">
-        <v>1826.1531</v>
+        <v>253538.5496226</v>
       </c>
       <c r="G26" t="n">
-        <v>367.5</v>
+        <v>1252.706172839506</v>
       </c>
       <c r="H26" t="n">
-        <v>117461.9166666667</v>
+        <v>614.2222222222222</v>
       </c>
       <c r="I26" t="n">
-        <v>0.8712546404650779</v>
+        <v>0.0919283919839063</v>
       </c>
     </row>
     <row r="27">
@@ -1354,23 +1354,23 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>C유형_기타일반가구</t>
+          <t>B유형_자산소득불일치</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>30</v>
+        <v>97</v>
       </c>
       <c r="F27" t="n">
-        <v>5387.3012</v>
+        <v>58437.2799391</v>
       </c>
       <c r="G27" t="n">
-        <v>3919.966666666667</v>
+        <v>986.2268041237113</v>
       </c>
       <c r="H27" t="n">
-        <v>49934.3</v>
+        <v>27601.03092783505</v>
       </c>
       <c r="I27" t="n">
-        <v>0.6753753144492652</v>
+        <v>0.7296176913739409</v>
       </c>
     </row>
     <row r="28">
@@ -1389,23 +1389,23 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>D유형_여유자산가층</t>
+          <t>C유형_기타일반가구</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>24</v>
+        <v>1188</v>
       </c>
       <c r="F28" t="n">
-        <v>4246.4246</v>
+        <v>860404.63782074</v>
       </c>
       <c r="G28" t="n">
-        <v>4699.083333333333</v>
+        <v>4007.556397306397</v>
       </c>
       <c r="H28" t="n">
-        <v>121222.9166666667</v>
+        <v>5390.619528619529</v>
       </c>
       <c r="I28" t="n">
-        <v>0.8702582108338525</v>
+        <v>0.3064446684960518</v>
       </c>
     </row>
     <row r="29">
@@ -1419,28 +1419,28 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>후기고령자(75+)</t>
+          <t>전기고령자(65-74)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>A유형_구조적취약층</t>
+          <t>D유형_여유자산가층</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>25</v>
+        <v>1007</v>
       </c>
       <c r="F29" t="n">
-        <v>4283.4071</v>
+        <v>756258.5658914699</v>
       </c>
       <c r="G29" t="n">
-        <v>1275.56</v>
+        <v>5814.758689175769</v>
       </c>
       <c r="H29" t="n">
-        <v>22923.84</v>
+        <v>31832.78152929493</v>
       </c>
       <c r="I29" t="n">
-        <v>0.4841812272060289</v>
+        <v>0.5731091803744084</v>
       </c>
     </row>
     <row r="30">
@@ -1459,23 +1459,23 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>B유형_자산소득불일치</t>
+          <t>A유형_구조적취약층</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>15</v>
+        <v>833</v>
       </c>
       <c r="F30" t="n">
-        <v>3077.4736</v>
+        <v>510270.9225125</v>
       </c>
       <c r="G30" t="n">
-        <v>813.6666666666666</v>
+        <v>1142.49699879952</v>
       </c>
       <c r="H30" t="n">
-        <v>117717.7333333333</v>
+        <v>783.0348139255702</v>
       </c>
       <c r="I30" t="n">
-        <v>0.8957146058718987</v>
+        <v>0.1676285048521</v>
       </c>
     </row>
     <row r="31">
@@ -1494,23 +1494,23 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>C유형_기타일반가구</t>
+          <t>B유형_자산소득불일치</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>46</v>
+        <v>237</v>
       </c>
       <c r="F31" t="n">
-        <v>8587.8452</v>
+        <v>136856.1956296</v>
       </c>
       <c r="G31" t="n">
-        <v>4297.673913043478</v>
+        <v>1063.324894514768</v>
       </c>
       <c r="H31" t="n">
-        <v>48790</v>
+        <v>25696.41350210971</v>
       </c>
       <c r="I31" t="n">
-        <v>0.6297357560793904</v>
+        <v>0.8459864697157458</v>
       </c>
     </row>
     <row r="32">
@@ -1529,23 +1529,58 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
+          <t>C유형_기타일반가구</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>918</v>
+      </c>
+      <c r="F32" t="n">
+        <v>601022.36524817</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2446.187363834423</v>
+      </c>
+      <c r="H32" t="n">
+        <v>6332.470588235294</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.4650516916932337</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>후기고령자(75+)</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
           <t>D유형_여유자산가층</t>
         </is>
       </c>
-      <c r="E32" t="n">
-        <v>30</v>
-      </c>
-      <c r="F32" t="n">
-        <v>5478.1984</v>
-      </c>
-      <c r="G32" t="n">
-        <v>5197.433333333333</v>
-      </c>
-      <c r="H32" t="n">
-        <v>120003.2666666667</v>
-      </c>
-      <c r="I32" t="n">
-        <v>0.8751436430367042</v>
+      <c r="E33" t="n">
+        <v>468</v>
+      </c>
+      <c r="F33" t="n">
+        <v>319762.0107266</v>
+      </c>
+      <c r="G33" t="n">
+        <v>4025.271367521368</v>
+      </c>
+      <c r="H33" t="n">
+        <v>29342.20085470086</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.6359935947225358</v>
       </c>
     </row>
   </sheetData>

--- a/sample_data/output/excel/02_수도권별_유형집계.xlsx
+++ b/sample_data/output/excel/02_수도권별_유형집계.xlsx
@@ -483,13 +483,13 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="F2" t="n">
-        <v>221678.271992234</v>
+        <v>161625.87763601</v>
       </c>
       <c r="G2" t="n">
-        <v>1228.11875</v>
+        <v>1023.925</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -518,19 +518,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="F3" t="n">
-        <v>97827.388699049</v>
+        <v>86258.60458914201</v>
       </c>
       <c r="G3" t="n">
-        <v>1043.192307692308</v>
+        <v>976.6666666666666</v>
       </c>
       <c r="H3" t="n">
-        <v>60660.25641025641</v>
+        <v>57871.21212121212</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8198865370873608</v>
+        <v>0.803838334519527</v>
       </c>
     </row>
     <row r="4">
@@ -553,19 +553,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>286</v>
+        <v>338</v>
       </c>
       <c r="F4" t="n">
-        <v>417916.658603107</v>
+        <v>489537.837069238</v>
       </c>
       <c r="G4" t="n">
-        <v>4157.898601398601</v>
+        <v>3786.082840236686</v>
       </c>
       <c r="H4" t="n">
-        <v>2566.783216783217</v>
+        <v>4870.118343195266</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1588162221035203</v>
+        <v>0.1666250276216928</v>
       </c>
     </row>
     <row r="5">
@@ -623,19 +623,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>244</v>
+        <v>199</v>
       </c>
       <c r="F6" t="n">
-        <v>298023.428483664</v>
+        <v>240637.076279988</v>
       </c>
       <c r="G6" t="n">
-        <v>1137.286885245902</v>
+        <v>1035.984924623116</v>
       </c>
       <c r="H6" t="n">
-        <v>75.40983606557377</v>
+        <v>72.36180904522612</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01601050521898927</v>
+        <v>0.01788310143958221</v>
       </c>
     </row>
     <row r="7">
@@ -658,19 +658,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="F7" t="n">
-        <v>174259.505781497</v>
+        <v>154367.769681979</v>
       </c>
       <c r="G7" t="n">
-        <v>825.2661870503597</v>
+        <v>752.390243902439</v>
       </c>
       <c r="H7" t="n">
-        <v>52548.43884892086</v>
+        <v>54725.47154471544</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8886940058553187</v>
+        <v>0.8890784619029551</v>
       </c>
     </row>
     <row r="8">
@@ -693,19 +693,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>140</v>
+        <v>201</v>
       </c>
       <c r="F8" t="n">
-        <v>177716.083009883</v>
+        <v>254994.171313077</v>
       </c>
       <c r="G8" t="n">
-        <v>2943.607142857143</v>
+        <v>2515.47263681592</v>
       </c>
       <c r="H8" t="n">
-        <v>7125</v>
+        <v>7833.333333333333</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3115993800869227</v>
+        <v>0.2892714193977687</v>
       </c>
     </row>
     <row r="9">
@@ -763,19 +763,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>442</v>
+        <v>326</v>
       </c>
       <c r="F10" t="n">
-        <v>272493.282306527</v>
+        <v>201865.202090605</v>
       </c>
       <c r="G10" t="n">
-        <v>1280.35294117647</v>
+        <v>1113.953987730061</v>
       </c>
       <c r="H10" t="n">
-        <v>690.5656108597285</v>
+        <v>683.9570552147239</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1233335738413891</v>
+        <v>0.1381606862347269</v>
       </c>
     </row>
     <row r="11">
@@ -798,19 +798,19 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="F11" t="n">
-        <v>84268.561814569</v>
+        <v>69658.371122376</v>
       </c>
       <c r="G11" t="n">
-        <v>959.2892561983471</v>
+        <v>855.1734693877551</v>
       </c>
       <c r="H11" t="n">
-        <v>25414.87603305785</v>
+        <v>25889.79591836735</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7364870671191805</v>
+        <v>0.7226507788769218</v>
       </c>
     </row>
     <row r="12">
@@ -833,19 +833,19 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1181</v>
+        <v>1320</v>
       </c>
       <c r="F12" t="n">
-        <v>857147.791811303</v>
+        <v>942386.062719418</v>
       </c>
       <c r="G12" t="n">
-        <v>3786.080440304826</v>
+        <v>3565.450757575758</v>
       </c>
       <c r="H12" t="n">
-        <v>5560.016934801016</v>
+        <v>5444.424242424242</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3331333397839507</v>
+        <v>0.3190899159103798</v>
       </c>
     </row>
     <row r="13">
@@ -903,19 +903,19 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>873</v>
+        <v>714</v>
       </c>
       <c r="F14" t="n">
-        <v>554035.945960442</v>
+        <v>448729.738417983</v>
       </c>
       <c r="G14" t="n">
-        <v>1136.154639175258</v>
+        <v>1017.058823529412</v>
       </c>
       <c r="H14" t="n">
-        <v>856.6254295532646</v>
+        <v>826.8039215686274</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1718875780098028</v>
+        <v>0.1795484384451862</v>
       </c>
     </row>
     <row r="15">
@@ -938,19 +938,19 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>245</v>
+        <v>221</v>
       </c>
       <c r="F15" t="n">
-        <v>147337.097776641</v>
+        <v>134205.715116072</v>
       </c>
       <c r="G15" t="n">
-        <v>1066.751020408163</v>
+        <v>1029.420814479638</v>
       </c>
       <c r="H15" t="n">
-        <v>26157.95918367347</v>
+        <v>26534.38914027149</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8248754063648499</v>
+        <v>0.817724042204263</v>
       </c>
     </row>
     <row r="16">
@@ -973,19 +973,19 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>813</v>
+        <v>996</v>
       </c>
       <c r="F16" t="n">
-        <v>540315.884052027</v>
+        <v>658753.474255055</v>
       </c>
       <c r="G16" t="n">
-        <v>2280.150061500615</v>
+        <v>2161.944779116466</v>
       </c>
       <c r="H16" t="n">
-        <v>6440.730627306273</v>
+        <v>5962.259036144578</v>
       </c>
       <c r="I16" t="n">
-        <v>0.484774659859344</v>
+        <v>0.4391159942274977</v>
       </c>
     </row>
     <row r="17">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="F18" t="n">
-        <v>205340.6416331</v>
+        <v>177446.8039887</v>
       </c>
       <c r="G18" t="n">
-        <v>1139.861842105263</v>
+        <v>1080.802919708029</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -1078,19 +1078,19 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="F19" t="n">
-        <v>100720.2935279</v>
+        <v>94278.5942489</v>
       </c>
       <c r="G19" t="n">
-        <v>1023.701298701299</v>
+        <v>982.9857142857143</v>
       </c>
       <c r="H19" t="n">
-        <v>50019.48051948052</v>
+        <v>49830</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8690255269303564</v>
+        <v>0.8699191319053154</v>
       </c>
     </row>
     <row r="20">
@@ -1113,19 +1113,19 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>305</v>
+        <v>327</v>
       </c>
       <c r="F20" t="n">
-        <v>436430.9360359</v>
+        <v>470766.4729593</v>
       </c>
       <c r="G20" t="n">
-        <v>4237.875409836066</v>
+        <v>4060.418960244648</v>
       </c>
       <c r="H20" t="n">
-        <v>3622.032786885246</v>
+        <v>4489.663608562691</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1831987803898601</v>
+        <v>0.189285181526522</v>
       </c>
     </row>
     <row r="21">
@@ -1183,19 +1183,19 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>245</v>
+        <v>212</v>
       </c>
       <c r="F22" t="n">
-        <v>290051.5625374</v>
+        <v>252621.6137809</v>
       </c>
       <c r="G22" t="n">
-        <v>1179.54693877551</v>
+        <v>1106.655660377359</v>
       </c>
       <c r="H22" t="n">
-        <v>104.4897959183673</v>
+        <v>75</v>
       </c>
       <c r="I22" t="n">
-        <v>0.02635643443269643</v>
+        <v>0.02216087301163626</v>
       </c>
     </row>
     <row r="23">
@@ -1218,19 +1218,19 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="F23" t="n">
-        <v>154685.0889611</v>
+        <v>141727.747213</v>
       </c>
       <c r="G23" t="n">
-        <v>1060.934959349594</v>
+        <v>1023.612612612613</v>
       </c>
       <c r="H23" t="n">
-        <v>49756.91056910569</v>
+        <v>51464.86486486487</v>
       </c>
       <c r="I23" t="n">
-        <v>0.9016057776266224</v>
+        <v>0.8936506896330868</v>
       </c>
     </row>
     <row r="24">
@@ -1253,19 +1253,19 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>158</v>
+        <v>203</v>
       </c>
       <c r="F24" t="n">
-        <v>201730.6259339</v>
+        <v>252117.9164385</v>
       </c>
       <c r="G24" t="n">
-        <v>2763.955696202532</v>
+        <v>2502.251231527094</v>
       </c>
       <c r="H24" t="n">
-        <v>8446.139240506329</v>
+        <v>8629.014778325123</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3166170131694451</v>
+        <v>0.3127438105276748</v>
       </c>
     </row>
     <row r="25">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>405</v>
+        <v>334</v>
       </c>
       <c r="F26" t="n">
-        <v>253538.5496226</v>
+        <v>208639.2036034</v>
       </c>
       <c r="G26" t="n">
-        <v>1252.706172839506</v>
+        <v>1127.739520958084</v>
       </c>
       <c r="H26" t="n">
-        <v>614.2222222222222</v>
+        <v>554.8802395209581</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0919283919839063</v>
+        <v>0.09405636969043346</v>
       </c>
     </row>
     <row r="27">
@@ -1358,19 +1358,19 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="F27" t="n">
-        <v>58437.2799391</v>
+        <v>53546.9197363</v>
       </c>
       <c r="G27" t="n">
-        <v>986.2268041237113</v>
+        <v>931.8505747126437</v>
       </c>
       <c r="H27" t="n">
-        <v>27601.03092783505</v>
+        <v>28436.7816091954</v>
       </c>
       <c r="I27" t="n">
-        <v>0.7296176913739409</v>
+        <v>0.7391344585781392</v>
       </c>
     </row>
     <row r="28">
@@ -1393,19 +1393,19 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1188</v>
+        <v>1269</v>
       </c>
       <c r="F28" t="n">
-        <v>860404.63782074</v>
+        <v>910194.3440427399</v>
       </c>
       <c r="G28" t="n">
-        <v>4007.556397306397</v>
+        <v>3866.234042553192</v>
       </c>
       <c r="H28" t="n">
-        <v>5390.619528619529</v>
+        <v>5256.726556343578</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3064446684960518</v>
+        <v>0.2965647404390552</v>
       </c>
     </row>
     <row r="29">
@@ -1463,19 +1463,19 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>833</v>
+        <v>735</v>
       </c>
       <c r="F30" t="n">
-        <v>510270.9225125</v>
+        <v>446103.2789713</v>
       </c>
       <c r="G30" t="n">
-        <v>1142.49699879952</v>
+        <v>1061.300680272109</v>
       </c>
       <c r="H30" t="n">
-        <v>783.0348139255702</v>
+        <v>769.6027210884354</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1676285048521</v>
+        <v>0.1690860860900798</v>
       </c>
     </row>
     <row r="31">
@@ -1498,19 +1498,19 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="F31" t="n">
-        <v>136856.1956296</v>
+        <v>126292.6037315</v>
       </c>
       <c r="G31" t="n">
-        <v>1063.324894514768</v>
+        <v>1029.677419354839</v>
       </c>
       <c r="H31" t="n">
-        <v>25696.41350210971</v>
+        <v>25702.99539170507</v>
       </c>
       <c r="I31" t="n">
-        <v>0.8459864697157458</v>
+        <v>0.8442475022472301</v>
       </c>
     </row>
     <row r="32">
@@ -1533,19 +1533,19 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>918</v>
+        <v>1036</v>
       </c>
       <c r="F32" t="n">
-        <v>601022.36524817</v>
+        <v>675753.6006874701</v>
       </c>
       <c r="G32" t="n">
-        <v>2446.187363834423</v>
+        <v>2360.822393822394</v>
       </c>
       <c r="H32" t="n">
-        <v>6332.470588235294</v>
+        <v>6189.496138996139</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4650516916932337</v>
+        <v>0.4436011675433996</v>
       </c>
     </row>
     <row r="33">
